--- a/input/ban.xlsx
+++ b/input/ban.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10706"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1/PycharmProjects/IMPORT BELTRAMI/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43777F97-B508-6243-92B5-3FF3B4DB8AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF95838-871E-7248-BAD0-393055EAE28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="1240" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>BLACK INC</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>MICHE</t>
+  </si>
+  <si>
+    <t>FEEDBACK</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -594,6 +597,11 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
